--- a/data/sars/pacific/tables/Pacific_2006_Appendix3.xlsx
+++ b/data/sars/pacific/tables/Pacific_2006_Appendix3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/marine_mammals/us_sar_synthesis/data/sars/pacific/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90445796-2BA7-7A45-B1F8-9732D220742C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2C9232C-A291-9442-9CD1-331B05C7FC36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="120" yWindow="500" windowWidth="32280" windowHeight="20180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Table 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Table 1'!$A$1:$O$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Table 1'!$A$1:$P$62</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="98">
   <si>
     <t>California sea lion</t>
   </si>
@@ -359,6 +359,12 @@
   </si>
   <si>
     <t>survey3</t>
+  </si>
+  <si>
+    <t>revised_yn</t>
+  </si>
+  <si>
+    <t>yes</t>
   </si>
 </sst>
 </file>
@@ -798,7 +804,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O62"/>
+  <dimension ref="A1:P62"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="16" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="36.59765625" style="2" bestFit="1" customWidth="1"/>
@@ -818,7 +824,7 @@
     <col min="20" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A1" s="17" t="s">
         <v>81</v>
       </c>
@@ -864,8 +870,11 @@
       <c r="O1" s="17" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="P1" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A2" s="18" t="s">
         <v>0</v>
       </c>
@@ -912,7 +921,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A3" s="19" t="s">
         <v>5</v>
       </c>
@@ -959,7 +968,7 @@
         <v>2004</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" s="19" t="s">
         <v>5</v>
       </c>
@@ -1002,7 +1011,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="19" t="s">
         <v>5</v>
       </c>
@@ -1045,7 +1054,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A6" s="19" t="s">
         <v>15</v>
       </c>
@@ -1092,7 +1101,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" s="19" t="s">
         <v>19</v>
       </c>
@@ -1135,7 +1144,7 @@
         <v>1993</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A8" s="21" t="s">
         <v>22</v>
       </c>
@@ -1181,8 +1190,11 @@
       <c r="O8" s="13">
         <v>2005</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="P8" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A9" s="21" t="s">
         <v>24</v>
       </c>
@@ -1228,8 +1240,11 @@
       <c r="O9" s="13">
         <v>2005</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="P9" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A10" s="19" t="s">
         <v>29</v>
       </c>
@@ -1276,7 +1291,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A11" s="19" t="s">
         <v>29</v>
       </c>
@@ -1323,7 +1338,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A12" s="19" t="s">
         <v>29</v>
       </c>
@@ -1370,7 +1385,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A13" s="19" t="s">
         <v>29</v>
       </c>
@@ -1417,7 +1432,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A14" s="21" t="s">
         <v>29</v>
       </c>
@@ -1463,8 +1478,11 @@
       <c r="O14" s="13">
         <v>2002</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="P14" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A15" s="21" t="s">
         <v>29</v>
       </c>
@@ -1510,8 +1528,11 @@
       <c r="O15" s="13">
         <v>2003</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="P15" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A16" s="19" t="s">
         <v>36</v>
       </c>
@@ -1558,7 +1579,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A17" s="19" t="s">
         <v>38</v>
       </c>
@@ -1605,7 +1626,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A18" s="19" t="s">
         <v>40</v>
       </c>
@@ -1652,7 +1673,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A19" s="21" t="s">
         <v>41</v>
       </c>
@@ -1698,8 +1719,11 @@
       <c r="O19" s="13">
         <v>2005</v>
       </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="P19" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A20" s="19" t="s">
         <v>41</v>
       </c>
@@ -1746,7 +1770,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A21" s="19" t="s">
         <v>44</v>
       </c>
@@ -1793,7 +1817,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A22" s="19" t="s">
         <v>45</v>
       </c>
@@ -1840,7 +1864,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A23" s="19" t="s">
         <v>46</v>
       </c>
@@ -1887,7 +1911,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A24" s="19" t="s">
         <v>47</v>
       </c>
@@ -1934,7 +1958,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A25" s="19" t="s">
         <v>48</v>
       </c>
@@ -1981,7 +2005,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A26" s="21" t="s">
         <v>48</v>
       </c>
@@ -2027,8 +2051,11 @@
       <c r="O26" s="13">
         <v>2005</v>
       </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="P26" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A27" s="19" t="s">
         <v>51</v>
       </c>
@@ -2075,7 +2102,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A28" s="19" t="s">
         <v>52</v>
       </c>
@@ -2122,7 +2149,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A29" s="19" t="s">
         <v>53</v>
       </c>
@@ -2169,7 +2196,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A30" s="19" t="s">
         <v>54</v>
       </c>
@@ -2216,7 +2243,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A31" s="19" t="s">
         <v>55</v>
       </c>
@@ -2263,7 +2290,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A32" s="19" t="s">
         <v>56</v>
       </c>
@@ -2310,7 +2337,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A33" s="19" t="s">
         <v>57</v>
       </c>
@@ -2357,7 +2384,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A34" s="19" t="s">
         <v>58</v>
       </c>
@@ -2404,7 +2431,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A35" s="19" t="s">
         <v>62</v>
       </c>
@@ -2451,7 +2478,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A36" s="19" t="s">
         <v>63</v>
       </c>
@@ -2498,7 +2525,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A37" s="19" t="s">
         <v>64</v>
       </c>
@@ -2545,7 +2572,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A38" s="19" t="s">
         <v>65</v>
       </c>
@@ -2592,7 +2619,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A39" s="19" t="s">
         <v>66</v>
       </c>
@@ -2639,7 +2666,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A40" s="19" t="s">
         <v>67</v>
       </c>
@@ -2684,7 +2711,7 @@
       </c>
       <c r="O40" s="16"/>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A41" s="19" t="s">
         <v>40</v>
       </c>
@@ -2729,7 +2756,7 @@
       </c>
       <c r="O41" s="16"/>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A42" s="21" t="s">
         <v>41</v>
       </c>
@@ -2773,8 +2800,11 @@
         <v>2004</v>
       </c>
       <c r="O42" s="16"/>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="P42" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A43" s="19" t="s">
         <v>68</v>
       </c>
@@ -2819,7 +2849,7 @@
       </c>
       <c r="O43" s="16"/>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A44" s="19" t="s">
         <v>69</v>
       </c>
@@ -2864,7 +2894,7 @@
       </c>
       <c r="O44" s="16"/>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A45" s="19" t="s">
         <v>44</v>
       </c>
@@ -2909,7 +2939,7 @@
       </c>
       <c r="O45" s="16"/>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A46" s="19" t="s">
         <v>70</v>
       </c>
@@ -2954,7 +2984,7 @@
       </c>
       <c r="O46" s="16"/>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A47" s="19" t="s">
         <v>71</v>
       </c>
@@ -2999,7 +3029,7 @@
       </c>
       <c r="O47" s="16"/>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A48" s="19" t="s">
         <v>72</v>
       </c>
@@ -3044,7 +3074,7 @@
       </c>
       <c r="O48" s="16"/>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A49" s="21" t="s">
         <v>73</v>
       </c>
@@ -3088,8 +3118,11 @@
         <v>2004</v>
       </c>
       <c r="O49" s="16"/>
-    </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="P49" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A50" s="19" t="s">
         <v>48</v>
       </c>
@@ -3134,7 +3167,7 @@
       </c>
       <c r="O50" s="16"/>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A51" s="21" t="s">
         <v>74</v>
       </c>
@@ -3178,8 +3211,11 @@
         <v>2004</v>
       </c>
       <c r="O51" s="16"/>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="P51" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A52" s="19" t="s">
         <v>75</v>
       </c>
@@ -3224,7 +3260,7 @@
       </c>
       <c r="O52" s="16"/>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A53" s="19" t="s">
         <v>76</v>
       </c>
@@ -3269,7 +3305,7 @@
       </c>
       <c r="O53" s="16"/>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A54" s="19" t="s">
         <v>54</v>
       </c>
@@ -3314,7 +3350,7 @@
       </c>
       <c r="O54" s="16"/>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A55" s="19" t="s">
         <v>77</v>
       </c>
@@ -3359,7 +3395,7 @@
       </c>
       <c r="O55" s="16"/>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A56" s="19" t="s">
         <v>56</v>
       </c>
@@ -3404,7 +3440,7 @@
       </c>
       <c r="O56" s="16"/>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A57" s="19" t="s">
         <v>57</v>
       </c>
@@ -3449,7 +3485,7 @@
       </c>
       <c r="O57" s="16"/>
     </row>
-    <row r="58" spans="1:15" ht="17" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:16" ht="17" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="19" t="s">
         <v>62</v>
       </c>
@@ -3494,7 +3530,7 @@
       </c>
       <c r="O58" s="16"/>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A59" s="19" t="s">
         <v>63</v>
       </c>
@@ -3539,7 +3575,7 @@
       </c>
       <c r="O59" s="16"/>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A60" s="19" t="s">
         <v>65</v>
       </c>
@@ -3584,7 +3620,7 @@
       </c>
       <c r="O60" s="16"/>
     </row>
-    <row r="61" spans="1:15" ht="17" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:16" ht="17" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="19" t="s">
         <v>66</v>
       </c>
@@ -3629,7 +3665,7 @@
       </c>
       <c r="O61" s="16"/>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A62" s="19" t="s">
         <v>64</v>
       </c>
@@ -3675,7 +3711,7 @@
       <c r="O62" s="16"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O62" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:P62" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>